--- a/data/trans_orig/IP07A07-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07A07-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2007 (tasa de respuesta: 99,6%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el adulto en 2007 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11715</t>
+          <t>11209</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13778</t>
+          <t>13141</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>12424</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16991</t>
+          <t>16614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13811</t>
+          <t>13447</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26764</t>
+          <t>25613</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25183</t>
+          <t>25905</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35997</t>
+          <t>36131</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22503</t>
+          <t>22281</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32364</t>
+          <t>32250</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>50953</t>
+          <t>51247</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64985</t>
+          <t>65449</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>861</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15492</t>
+          <t>15383</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10257</t>
+          <t>10347</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11290</t>
+          <t>11952</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22612</t>
+          <t>22839</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>37,04%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10807</t>
+          <t>11146</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19795</t>
+          <t>19375</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19980</t>
+          <t>20102</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27956</t>
+          <t>27821</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33242</t>
+          <t>32996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45280</t>
+          <t>45229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,36%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>10273</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10445</t>
+          <t>10429</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>7515</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17803</t>
+          <t>18199</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5251</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13428</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14691</t>
+          <t>14736</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27802</t>
+          <t>26794</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13644</t>
+          <t>13450</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22814</t>
+          <t>22421</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31407</t>
+          <t>31381</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42375</t>
+          <t>42284</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47681</t>
+          <t>47542</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62306</t>
+          <t>62101</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>70,94%</t>
         </is>
       </c>
     </row>
@@ -2778,82 +2778,82 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5888</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>6,6%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>645</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5528</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>6,2%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2034</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15990</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18997</t>
+          <t>18435</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16786</t>
+          <t>16263</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31859</t>
+          <t>31124</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18630</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33096</t>
+          <t>33201</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17834</t>
+          <t>17053</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30886</t>
+          <t>31083</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40003</t>
+          <t>39837</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60561</t>
+          <t>59559</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41987</t>
+          <t>41467</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>56743</t>
+          <t>56516</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48362</t>
+          <t>47130</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>63000</t>
+          <t>63165</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>93523</t>
+          <t>93740</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>115081</t>
+          <t>115634</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>63,17%</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>631</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14829</t>
+          <t>14220</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13490</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24039</t>
+          <t>24274</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7888</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18287</t>
+          <t>18159</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>22887</t>
+          <t>22820</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>21173</t>
+          <t>21260</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>36342</t>
+          <t>36223</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>25619</t>
+          <t>25929</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>37686</t>
+          <t>37991</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>37348</t>
+          <t>36996</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>50021</t>
+          <t>50358</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>66495</t>
+          <t>67501</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>84838</t>
+          <t>85265</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,43%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9345</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14528</t>
+          <t>14954</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9962</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>10420</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>21422</t>
+          <t>21722</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>23136</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>32799</t>
+          <t>33405</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>25216</t>
+          <t>25301</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>32597</t>
+          <t>32099</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>50685</t>
+          <t>50346</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>63098</t>
+          <t>62766</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>80,84%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1391</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>8857</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>8826</t>
+          <t>8158</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>30942</t>
+          <t>30649</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>49725</t>
+          <t>49834</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>23339</t>
+          <t>22860</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>40977</t>
+          <t>39912</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>58604</t>
+          <t>59256</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>84637</t>
+          <t>83942</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>62832</t>
+          <t>63751</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>87560</t>
+          <t>87631</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>64030</t>
+          <t>62257</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>87512</t>
+          <t>85753</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>132888</t>
+          <t>132724</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>168487</t>
+          <t>166923</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>160524</t>
+          <t>158932</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>188020</t>
+          <t>186189</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>203805</t>
+          <t>204738</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>230030</t>
+          <t>230724</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>371931</t>
+          <t>372319</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>411438</t>
+          <t>412182</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,2%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2012 (tasa de respuesta: 98,23%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el adulto en 2012 (tasa de respuesta: 98,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>9986</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13071</t>
+          <t>12336</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8758</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20023</t>
+          <t>19450</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6814</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16466</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11045</t>
+          <t>11341</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12131</t>
+          <t>12396</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25005</t>
+          <t>24546</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16871</t>
+          <t>17064</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27463</t>
+          <t>27613</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13067</t>
+          <t>13670</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23042</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33786</t>
+          <t>34047</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>47814</t>
+          <t>47659</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,06%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>11847</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>16327</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11528</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23467</t>
+          <t>23861</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>34,18%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11514</t>
+          <t>11139</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20553</t>
+          <t>20630</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22221</t>
+          <t>21642</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30004</t>
+          <t>29914</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35533</t>
+          <t>35273</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49360</t>
+          <t>48909</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,05%</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13057</t>
+          <t>13002</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>9704</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6590</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15181</t>
+          <t>15382</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18673</t>
+          <t>18913</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31945</t>
+          <t>32688</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>42,83%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18823</t>
+          <t>18736</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29562</t>
+          <t>29481</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12866</t>
+          <t>12687</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21930</t>
+          <t>21543</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>34241</t>
+          <t>34342</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>48135</t>
+          <t>48595</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,67%</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>663</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>582</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>8992</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16649</t>
+          <t>16309</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11010</t>
+          <t>11355</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23933</t>
+          <t>24299</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>19593</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>36767</t>
+          <t>35373</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13068</t>
+          <t>12753</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25409</t>
+          <t>26638</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>12929</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26478</t>
+          <t>26287</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29284</t>
+          <t>28986</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>46936</t>
+          <t>46495</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47560</t>
+          <t>46876</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>62045</t>
+          <t>61522</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>53103</t>
+          <t>53795</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69186</t>
+          <t>69881</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>106153</t>
+          <t>104193</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>127875</t>
+          <t>126693</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>67,76%</t>
         </is>
       </c>
     </row>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12300</t>
+          <t>12512</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16912</t>
+          <t>16475</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12404</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>25809</t>
+          <t>25595</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16385</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>29359</t>
+          <t>29183</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13005</t>
+          <t>13195</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>25291</t>
+          <t>25185</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>31831</t>
+          <t>31931</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>50339</t>
+          <t>50530</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>35940</t>
+          <t>36190</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>50023</t>
+          <t>50363</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>34526</t>
+          <t>34162</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>47426</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>73617</t>
+          <t>74005</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>94618</t>
+          <t>94338</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,68%</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>635</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>11902</t>
+          <t>11251</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5097</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>14302</t>
+          <t>14526</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11445</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10870</t>
+          <t>11003</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>8634</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>19200</t>
+          <t>19204</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>10632</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>18581</t>
+          <t>19142</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>18690</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>28242</t>
+          <t>28615</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>32425</t>
+          <t>31586</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>45088</t>
+          <t>44695</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>71,75%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>8327</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>13183</t>
+          <t>13038</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>14605</t>
+          <t>14572</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>771</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>6996</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>17810</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>25857</t>
+          <t>25020</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>42643</t>
+          <t>43094</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>40150</t>
+          <t>40016</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>61832</t>
+          <t>62558</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>71253</t>
+          <t>70209</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>99167</t>
+          <t>98696</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>72579</t>
+          <t>71687</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>98904</t>
+          <t>99562</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>57029</t>
+          <t>55934</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>80275</t>
+          <t>79272</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>135074</t>
+          <t>135342</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>170853</t>
+          <t>170281</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>160632</t>
+          <t>160743</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>189431</t>
+          <t>189665</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>174790</t>
+          <t>175575</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>203757</t>
+          <t>202239</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>343991</t>
+          <t>344628</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>382639</t>
+          <t>384862</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,28%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>580</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6704</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>12072</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>11787</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15906</t>
+          <t>15867</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12689</t>
+          <t>13175</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24805</t>
+          <t>24949</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,22%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17645</t>
+          <t>17683</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26450</t>
+          <t>26768</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14810</t>
+          <t>14393</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24435</t>
+          <t>24995</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35632</t>
+          <t>35287</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49455</t>
+          <t>48930</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,11%</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>765</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8574</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8981</t>
+          <t>9366</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8573</t>
+          <t>7912</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19318</t>
+          <t>18649</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13851</t>
+          <t>14017</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15384</t>
+          <t>15712</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29612</t>
+          <t>29579</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23734</t>
+          <t>24204</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35692</t>
+          <t>36372</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27545</t>
+          <t>27303</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37844</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54025</t>
+          <t>55080</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70759</t>
+          <t>71531</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>70,88%</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2933</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>970</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>9337</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>8971</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15898</t>
+          <t>15712</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10633</t>
+          <t>10457</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21942</t>
+          <t>21955</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15387</t>
+          <t>15304</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23550</t>
+          <t>23421</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22598</t>
+          <t>22067</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32603</t>
+          <t>32222</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40966</t>
+          <t>40440</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53439</t>
+          <t>53064</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,6%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>651</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7656</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>13088</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>5685</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16496</t>
+          <t>16260</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17511</t>
+          <t>17572</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14817</t>
+          <t>14180</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13532</t>
+          <t>13985</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27025</t>
+          <t>28339</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16241</t>
+          <t>15962</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30348</t>
+          <t>30403</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13251</t>
+          <t>13049</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26002</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32853</t>
+          <t>32978</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52219</t>
+          <t>51691</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>64514</t>
+          <t>64382</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>80935</t>
+          <t>81078</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>62156</t>
+          <t>61001</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>77528</t>
+          <t>77711</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>130400</t>
+          <t>131625</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>154788</t>
+          <t>153951</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,41%</t>
         </is>
       </c>
     </row>
@@ -13481,7 +13481,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>641</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6576</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16380</t>
+          <t>16966</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8918</t>
+          <t>8826</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9266</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22125</t>
+          <t>21513</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2284</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9493</t>
+          <t>9635</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t>9733</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15578</t>
+          <t>15658</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11240</t>
+          <t>11132</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>23894</t>
+          <t>23797</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12711</t>
+          <t>12334</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24497</t>
+          <t>24738</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>27116</t>
+          <t>26358</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>44579</t>
+          <t>42361</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>36179</t>
+          <t>35758</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>50473</t>
+          <t>50293</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>36498</t>
+          <t>37274</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>50533</t>
+          <t>51100</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>78564</t>
+          <t>78446</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>98333</t>
+          <t>97834</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,4%</t>
         </is>
       </c>
     </row>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>6893</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -14311,7 +14311,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>728</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>8911</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12581</t>
+          <t>13334</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13874</t>
+          <t>14772</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>12211</t>
+          <t>12107</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>24419</t>
+          <t>23966</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>33,83%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>16012</t>
+          <t>15792</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>24964</t>
+          <t>24588</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>19353</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>28973</t>
+          <t>28829</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38491</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>51227</t>
+          <t>51275</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,37%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7660</t>
+          <t>7257</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>13853</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>7383</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>17514</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>14271</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>29156</t>
+          <t>28470</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>21379</t>
+          <t>22473</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15008,7 +15008,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>27155</t>
+          <t>26993</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>47194</t>
+          <t>47011</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>23935</t>
+          <t>24209</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>41292</t>
+          <t>41275</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>16906</t>
+          <t>16404</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>33113</t>
+          <t>32476</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>44381</t>
+          <t>43719</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>67391</t>
+          <t>66637</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>60689</t>
+          <t>60669</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>87244</t>
+          <t>85723</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>64373</t>
+          <t>65244</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>88767</t>
+          <t>90989</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>131623</t>
+          <t>131522</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>167362</t>
+          <t>169989</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,95%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>192951</t>
+          <t>195070</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>224297</t>
+          <t>225540</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>203367</t>
+          <t>203179</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>233090</t>
+          <t>233352</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>406891</t>
+          <t>406317</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>450620</t>
+          <t>450712</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,15%</t>
         </is>
       </c>
     </row>
